--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2021_la_araucania_sexo.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2021_la_araucania_sexo.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:38</t>
+    <t xml:space="preserve">2026-09-09 20:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2021_la_araucania_sexo.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2021_la_araucania_sexo.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Serie_neta" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Serie_neta'!$A$1:$D$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Serie_neta'!$A$1:$D$57</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:40</t>
+    <t xml:space="preserve">2026-09-18 10:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -937,16 +937,16 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>65.71</v>
+        <v>58.44</v>
       </c>
     </row>
     <row r="12">
@@ -957,24 +957,24 @@
         <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>59.47</v>
+        <v>65.71</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>67.84</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="14">
@@ -985,24 +985,24 @@
         <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>60.87</v>
+        <v>67.84</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>96.45</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="16">
@@ -1013,24 +1013,24 @@
         <v>10</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>95.14</v>
+        <v>96.45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>96.41</v>
+        <v>95.14</v>
       </c>
     </row>
     <row r="18">
@@ -1041,24 +1041,24 @@
         <v>10</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>95.11</v>
+        <v>96.41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>96.47</v>
+        <v>95.11</v>
       </c>
     </row>
     <row r="20">
@@ -1069,24 +1069,24 @@
         <v>10</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>95.21</v>
+        <v>96.47</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>96.36</v>
+        <v>95.21</v>
       </c>
     </row>
     <row r="22">
@@ -1097,29 +1097,29 @@
         <v>10</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>94.65</v>
+        <v>96.36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>96.13</v>
+        <v>94.65</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>10</v>
@@ -1128,12 +1128,12 @@
         <v>25</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>95.9</v>
+        <v>96.13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>10</v>
@@ -1142,12 +1142,12 @@
         <v>26</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>93.93</v>
+        <v>94.28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>10</v>
@@ -1156,12 +1156,12 @@
         <v>25</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>95.79</v>
+        <v>95.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>10</v>
@@ -1170,40 +1170,40 @@
         <v>26</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>93.43</v>
+        <v>93.93</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>83.49</v>
+        <v>95.79</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>82.27</v>
+        <v>93.43</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>9</v>
@@ -1212,12 +1212,12 @@
         <v>25</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>84.72</v>
+        <v>83.49</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>9</v>
@@ -1226,12 +1226,12 @@
         <v>26</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>83.18</v>
+        <v>82.27</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>9</v>
@@ -1240,12 +1240,12 @@
         <v>25</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>86.16</v>
+        <v>84.72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>9</v>
@@ -1254,12 +1254,12 @@
         <v>26</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>84.48</v>
+        <v>83.18</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>9</v>
@@ -1268,12 +1268,12 @@
         <v>25</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>88.14</v>
+        <v>86.16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>9</v>
@@ -1282,12 +1282,12 @@
         <v>26</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>86.23</v>
+        <v>84.48</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>9</v>
@@ -1296,194 +1296,194 @@
         <v>25</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>88.89</v>
+        <v>88.14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>88.75</v>
+        <v>86.23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>86.9</v>
+        <v>88.89</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>89.27</v>
+        <v>86.91</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>86.94</v>
+        <v>88.75</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>38.67</v>
+        <v>86.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>41.13</v>
+        <v>89.27</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>39.58</v>
+        <v>86.94</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>41.9</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>39.92</v>
+        <v>41.13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>42.47</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>40.61</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>42.64</v>
+        <v>39.92</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>41.21</v>
+        <v>42.47</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>4</v>
@@ -1492,12 +1492,12 @@
         <v>25</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>42.95</v>
+        <v>40.61</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>4</v>
@@ -1506,12 +1506,12 @@
         <v>26</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>45.8</v>
+        <v>42.64</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>4</v>
@@ -1520,25 +1520,81 @@
         <v>25</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>45.15</v>
+        <v>41.21</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>43.38</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>42.95</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>45.8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D53" s="2" t="n">
+      <c r="B56" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>45.15</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D57" s="2" t="n">
         <v>47.83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D53"/>
+  <autoFilter ref="A1:D57"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2021_la_araucania_sexo.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2021_la_araucania_sexo.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:31</t>
+    <t xml:space="preserve">2026-09-23 16:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2021_la_araucania_sexo.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2021_la_araucania_sexo.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 16:15</t>
+    <t xml:space="preserve">2026-10-05 05:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
